--- a/outputs/monitor_xlsx/20260205.xlsx
+++ b/outputs/monitor_xlsx/20260205.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1107,40 +1110,35 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1190,12 +1188,7 @@
       <c r="N4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1233,12 +1226,7 @@
       <c r="M5" t="n">
         <v>-30108</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1291,12 +1279,7 @@
       <c r="N6" t="n">
         <v>-1.85</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1349,12 +1332,7 @@
       <c r="N7" t="n">
         <v>-9.779999999999999</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1407,12 +1385,7 @@
       <c r="N8" t="n">
         <v>-5.35</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1465,12 +1438,7 @@
       <c r="N9" t="n">
         <v>-1.18</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1523,12 +1491,7 @@
       <c r="N10" t="n">
         <v>-12.91</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1581,12 +1544,7 @@
       <c r="N11" t="n">
         <v>5.81</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1639,12 +1597,7 @@
       <c r="N12" t="n">
         <v>-0.09</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1697,12 +1650,7 @@
       <c r="N13" t="n">
         <v>1.39</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1755,12 +1703,7 @@
       <c r="N14" t="n">
         <v>-1.52</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1813,12 +1756,7 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1871,12 +1809,7 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1929,12 +1862,7 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1987,12 +1915,7 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2045,12 +1968,7 @@
       <c r="N19" t="n">
         <v>6.46</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2103,11 +2021,6 @@
       <c r="N20" t="n">
         <v>-2.88</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2156,11 +2069,6 @@
       <c r="N21" t="n">
         <v>5.35</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2203,11 +2111,6 @@
       <c r="N22" t="n">
         <v>-7.04</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2256,11 +2159,6 @@
       <c r="N23" t="n">
         <v>-4.1</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2309,11 +2207,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2362,11 +2255,6 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2415,11 +2303,6 @@
       <c r="N26" t="n">
         <v>-3.22</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2467,11 +2350,6 @@
       </c>
       <c r="N27" t="n">
         <v>9.35</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260205.xlsx
+++ b/outputs/monitor_xlsx/20260205.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1152,41 +1149,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>-1.23</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="7" t="n">
         <v>107575</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="7" t="n">
         <v>-48799</v>
       </c>
-      <c r="G4" t="n">
-        <v>-187416</v>
+      <c r="H4" t="n">
+        <v>-207936</v>
       </c>
       <c r="I4" t="n">
-        <v>3445</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>1745</v>
+      </c>
+      <c r="K4" t="n">
         <v>28791</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7823</v>
       </c>
-      <c r="L4" t="n">
-        <v>37627</v>
-      </c>
       <c r="M4" t="n">
+        <v>38388</v>
+      </c>
+      <c r="N4" t="n">
         <v>-4015266</v>
       </c>
-      <c r="N4" t="n">
-        <v>-1.02</v>
+      <c r="O4" t="n">
+        <v>-0.04</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1243,41 +1248,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>955</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>-3.63</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="7" t="n">
         <v>4041</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="7" t="n">
         <v>-738</v>
       </c>
-      <c r="G6" t="n">
-        <v>-33</v>
-      </c>
       <c r="H6" t="n">
+        <v>-945</v>
+      </c>
+      <c r="I6" t="n">
         <v>49</v>
       </c>
-      <c r="I6" t="n">
-        <v>-238</v>
-      </c>
       <c r="J6" t="n">
+        <v>-248</v>
+      </c>
+      <c r="K6" t="n">
         <v>142</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2891</v>
       </c>
-      <c r="L6" t="n">
-        <v>13553</v>
-      </c>
       <c r="M6" t="n">
+        <v>13705</v>
+      </c>
+      <c r="N6" t="n">
         <v>-78716</v>
       </c>
-      <c r="N6" t="n">
-        <v>-1.85</v>
+      <c r="O6" t="n">
+        <v>-0.41</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1349,41 +1359,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1150</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>-4.96</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="7" t="n">
         <v>15861</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>-6112</v>
       </c>
-      <c r="G8" t="n">
-        <v>-995</v>
-      </c>
       <c r="H8" t="n">
+        <v>-6161</v>
+      </c>
+      <c r="I8" t="n">
         <v>-39</v>
       </c>
-      <c r="I8" t="n">
-        <v>-928</v>
-      </c>
       <c r="J8" t="n">
+        <v>-1023</v>
+      </c>
+      <c r="K8" t="n">
         <v>1097</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>6102</v>
       </c>
-      <c r="L8" t="n">
-        <v>31719</v>
-      </c>
       <c r="M8" t="n">
+        <v>31067</v>
+      </c>
+      <c r="N8" t="n">
         <v>-648674</v>
       </c>
-      <c r="N8" t="n">
-        <v>-5.35</v>
+      <c r="O8" t="n">
+        <v>-0.88</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1402,41 +1417,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1765</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>-1.12</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="7" t="n">
         <v>28974</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="G9" s="7" t="n">
         <v>-9668</v>
       </c>
-      <c r="G9" t="n">
-        <v>-44761</v>
-      </c>
       <c r="H9" t="n">
+        <v>-45800</v>
+      </c>
+      <c r="I9" t="n">
         <v>1236</v>
       </c>
-      <c r="I9" t="n">
-        <v>4434</v>
-      </c>
       <c r="J9" t="n">
+        <v>5654</v>
+      </c>
+      <c r="K9" t="n">
         <v>1003</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>23121</v>
       </c>
-      <c r="L9" t="n">
-        <v>105621</v>
-      </c>
       <c r="M9" t="n">
+        <v>108835</v>
+      </c>
+      <c r="N9" t="n">
         <v>-6482892</v>
       </c>
-      <c r="N9" t="n">
-        <v>-1.18</v>
+      <c r="O9" t="n">
+        <v>0.64</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1508,41 +1528,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>1950</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>-4.41</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="7" t="n">
         <v>5986</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>-752</v>
       </c>
-      <c r="G11" t="n">
-        <v>767</v>
-      </c>
       <c r="H11" t="n">
+        <v>349</v>
+      </c>
+      <c r="I11" t="n">
         <v>172</v>
       </c>
-      <c r="I11" t="n">
-        <v>407</v>
-      </c>
       <c r="J11" t="n">
+        <v>1020</v>
+      </c>
+      <c r="K11" t="n">
         <v>277</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>2153</v>
       </c>
-      <c r="L11" t="n">
-        <v>10303</v>
-      </c>
       <c r="M11" t="n">
+        <v>10403</v>
+      </c>
+      <c r="N11" t="n">
         <v>-89504</v>
       </c>
-      <c r="N11" t="n">
-        <v>5.81</v>
+      <c r="O11" t="n">
+        <v>12.99</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1667,41 +1692,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>1755</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>-5.65</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="6" t="n">
         <v>1143</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
-        <v>2542</v>
-      </c>
       <c r="H14" t="n">
+        <v>538</v>
+      </c>
+      <c r="I14" t="n">
         <v>-74</v>
       </c>
-      <c r="I14" t="n">
-        <v>-65</v>
-      </c>
       <c r="J14" t="n">
+        <v>-292</v>
+      </c>
+      <c r="K14" t="n">
         <v>11</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4398</v>
       </c>
-      <c r="L14" t="n">
-        <v>21753</v>
-      </c>
       <c r="M14" t="n">
+        <v>21623</v>
+      </c>
+      <c r="N14" t="n">
         <v>-19229</v>
       </c>
-      <c r="N14" t="n">
-        <v>-1.52</v>
+      <c r="O14" t="n">
+        <v>19.14</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1720,42 +1750,47 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="E15" t="n">
-        <v>905</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>2.16</v>
       </c>
       <c r="F15" s="6" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="G15" t="n">
-        <v>2840</v>
-      </c>
       <c r="H15" t="n">
+        <v>1513</v>
+      </c>
+      <c r="I15" t="n">
         <v>-5</v>
       </c>
-      <c r="I15" t="n">
-        <v>-126</v>
-      </c>
       <c r="J15" t="n">
+        <v>-133</v>
+      </c>
+      <c r="K15" t="n">
         <v>22</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-169</v>
       </c>
-      <c r="L15" t="n">
-        <v>-1390</v>
-      </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-881</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1879,42 +1914,47 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>318.5</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="E18" t="n">
-        <v>20497</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>586</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>9.94</v>
       </c>
       <c r="F18" s="6" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="6" t="n">
         <v>1022</v>
       </c>
-      <c r="G18" t="n">
-        <v>1720</v>
-      </c>
       <c r="H18" t="n">
+        <v>282</v>
+      </c>
+      <c r="I18" t="n">
         <v>1592</v>
       </c>
-      <c r="I18" t="n">
-        <v>4478</v>
-      </c>
       <c r="J18" t="n">
+        <v>3562</v>
+      </c>
+      <c r="K18" t="n">
         <v>-46</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-1396</v>
       </c>
-      <c r="L18" t="n">
-        <v>-241</v>
-      </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-666</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2123,41 +2163,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
         <v>1125</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>-5.06</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="7" t="n">
         <v>3576</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="G23" s="7" t="n">
         <v>-1094</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>-1893</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-180</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-223</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>171</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2718</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>13347</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140153</v>
       </c>
-      <c r="N23" t="n">
-        <v>-4.1</v>
+      <c r="O23" t="n">
+        <v>-4.28</v>
       </c>
     </row>
     <row r="24">
@@ -2171,42 +2216,47 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>-20</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-81</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-5</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-6</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-106</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2219,42 +2269,47 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>624</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2040</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-2.64</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>-898</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>451</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>-13</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>-60</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>60</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-105</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2267,41 +2322,46 @@
           <t>致茂</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
         <v>974</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>-5.44</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" s="7" t="n">
         <v>3158</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="G26" s="7" t="n">
         <v>-490</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-402</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>-67</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>168</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>149</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>940</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>4473</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-106282</v>
       </c>
-      <c r="N26" t="n">
-        <v>-3.22</v>
+      <c r="O26" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="27">
@@ -2350,6 +2410,112 @@
       </c>
       <c r="N27" t="n">
         <v>9.35</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>4425</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>509</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>378</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" t="n">
+        <v>333</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1762</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-8870</v>
+      </c>
+      <c r="O28" t="n">
+        <v>14.59</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>208.5</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>-47</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-1112</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-139</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-397</v>
+      </c>
+      <c r="K29" t="n">
+        <v>19</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6141</v>
+      </c>
+      <c r="M29" t="n">
+        <v>30574</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-21789</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-6.69</v>
       </c>
     </row>
   </sheetData>
